--- a/scratch for consolidation.xlsx
+++ b/scratch for consolidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristinamensik/Library/Mobile Documents/com~apple~CloudDocs/Documents/Duke/2024-2025/902 Legislators Pre-Ananlysis Plan/Prelim Folder/Prelim 3-23/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kom11/Documents/GitHub/phd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAEC1CD-9E24-224F-81C4-8B208E9A5359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9AC4B1-B1FD-B943-BC80-90215EC2069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16160" yWindow="500" windowWidth="24640" windowHeight="22300" xr2:uid="{1485591A-AD4E-AF48-B5E4-0AC801435F7E}"/>
+    <workbookView xWindow="9560" yWindow="680" windowWidth="24640" windowHeight="21460" xr2:uid="{1485591A-AD4E-AF48-B5E4-0AC801435F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1342,7 +1342,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1818,7 +1817,7 @@
     <col min="5" max="5" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>210</v>
       </c>
